--- a/docentes/Castro Vasquez Julieta - Estadisticos 20211.xlsx
+++ b/docentes/Castro Vasquez Julieta - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="30">
   <si>
     <t>Mat</t>
   </si>
@@ -79,67 +79,34 @@
     <t>BACILIO</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>XILCAHUA</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
+    <t>VILLALBA</t>
   </si>
   <si>
     <t>ATILANO</t>
   </si>
   <si>
+    <t>IXTLA</t>
+  </si>
+  <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>GUZMAN</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
-    <t>JAIR</t>
+    <t>ADAN</t>
   </si>
   <si>
     <t>YAIR</t>
   </si>
   <si>
+    <t>ELIEL</t>
+  </si>
+  <si>
     <t>EVELYN</t>
-  </si>
-  <si>
-    <t>ALEXIS MANUEL</t>
-  </si>
-  <si>
-    <t>JESUS HAZAEL</t>
-  </si>
-  <si>
-    <t>EDGAR DANIEL</t>
-  </si>
-  <si>
-    <t>EMILIO</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
   </si>
 </sst>
 </file>
@@ -540,19 +507,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G2">
-        <v>38.89</v>
+        <v>58.33</v>
       </c>
       <c r="H2">
-        <v>8.9</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -566,19 +533,19 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>74.36</v>
+        <v>82.05</v>
       </c>
       <c r="H3">
-        <v>9.300000000000001</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -592,19 +559,19 @@
         <v>24</v>
       </c>
       <c r="D4">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G4">
-        <v>33.33</v>
+        <v>54.17</v>
       </c>
       <c r="H4">
-        <v>8.9</v>
+        <v>6.8</v>
       </c>
     </row>
   </sheetData>
@@ -657,16 +624,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>55.56</v>
+      </c>
+      <c r="H2">
+        <v>6.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -680,16 +650,19 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>84.62</v>
+      </c>
+      <c r="H3">
+        <v>8.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -703,16 +676,19 @@
         <v>24</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>45.83</v>
+      </c>
+      <c r="H4">
+        <v>6.8</v>
       </c>
     </row>
   </sheetData>
@@ -765,19 +741,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>38.89</v>
+        <v>55.56</v>
       </c>
       <c r="H2">
-        <v>8.9</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -791,19 +767,19 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G3">
-        <v>74.36</v>
+        <v>84.62</v>
       </c>
       <c r="H3">
-        <v>9.300000000000001</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -817,19 +793,19 @@
         <v>24</v>
       </c>
       <c r="D4">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F4">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G4">
-        <v>33.33</v>
+        <v>45.83</v>
       </c>
       <c r="H4">
-        <v>8.9</v>
+        <v>6.8</v>
       </c>
     </row>
   </sheetData>
@@ -839,7 +815,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -871,25 +847,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920361</v>
+        <v>20330051920337</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" t="s">
         <v>26</v>
       </c>
-      <c r="D2" t="s">
-        <v>33</v>
-      </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -900,10 +876,10 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
         <v>27</v>
-      </c>
-      <c r="D3" t="s">
-        <v>34</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -912,21 +888,21 @@
         <v>11</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920347</v>
+        <v>20330051920345</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
       </c>
       <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
         <v>28</v>
-      </c>
-      <c r="D4" t="s">
-        <v>35</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -935,122 +911,30 @@
         <v>11</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920014</v>
+        <v>20330051920347</v>
       </c>
       <c r="B5" t="s">
         <v>21</v>
       </c>
       <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
         <v>29</v>
       </c>
-      <c r="D5" t="s">
-        <v>36</v>
-      </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920023</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920381</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920352</v>
-      </c>
-      <c r="B8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920357</v>
-      </c>
-      <c r="B9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Castro Vasquez Julieta - Estadisticos 20211.xlsx
+++ b/docentes/Castro Vasquez Julieta - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="33">
   <si>
     <t>Mat</t>
   </si>
@@ -76,6 +76,9 @@
     <t>BARRAGAN</t>
   </si>
   <si>
+    <t>CUEVAS</t>
+  </si>
+  <si>
     <t>BACILIO</t>
   </si>
   <si>
@@ -88,6 +91,9 @@
     <t>VILLALBA</t>
   </si>
   <si>
+    <t>CUATRA</t>
+  </si>
+  <si>
     <t>ATILANO</t>
   </si>
   <si>
@@ -98,6 +104,9 @@
   </si>
   <si>
     <t>ADAN</t>
+  </si>
+  <si>
+    <t>CESAR</t>
   </si>
   <si>
     <t>YAIR</t>
@@ -815,7 +824,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -853,10 +862,10 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -865,21 +874,21 @@
         <v>11</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920336</v>
+        <v>20330051920340</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -893,16 +902,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920345</v>
+        <v>20330051920336</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -911,21 +920,21 @@
         <v>11</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920347</v>
+        <v>20330051920345</v>
       </c>
       <c r="B5" t="s">
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -934,7 +943,30 @@
         <v>11</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>20330051920347</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Castro Vasquez Julieta - Estadisticos 20211.xlsx
+++ b/docentes/Castro Vasquez Julieta - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="39">
   <si>
     <t>Mat</t>
   </si>
@@ -73,12 +73,18 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
     <t>BARRAGAN</t>
   </si>
   <si>
     <t>CUEVAS</t>
   </si>
   <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
     <t>BACILIO</t>
   </si>
   <si>
@@ -88,12 +94,18 @@
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>TORRES</t>
+  </si>
+  <si>
     <t>VILLALBA</t>
   </si>
   <si>
     <t>CUATRA</t>
   </si>
   <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
     <t>ATILANO</t>
   </si>
   <si>
@@ -103,10 +115,16 @@
     <t>DE JESUS</t>
   </si>
   <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
     <t>ADAN</t>
   </si>
   <si>
     <t>CESAR</t>
+  </si>
+  <si>
+    <t>OCTAVIO</t>
   </si>
   <si>
     <t>YAIR</t>
@@ -824,7 +842,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -856,39 +874,39 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920337</v>
+        <v>20330051920003</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920340</v>
+        <v>20330051920337</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -902,16 +920,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920336</v>
+        <v>20330051920340</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -920,27 +938,27 @@
         <v>11</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920345</v>
+        <v>20330051920021</v>
       </c>
       <c r="B5" t="s">
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -948,16 +966,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920347</v>
+        <v>20330051920336</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -966,6 +984,52 @@
         <v>11</v>
       </c>
       <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>20330051920345</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>20330051920347</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Castro Vasquez Julieta - Estadisticos 20211.xlsx
+++ b/docentes/Castro Vasquez Julieta - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="44">
   <si>
     <t>Mat</t>
   </si>
@@ -76,6 +76,12 @@
     <t>BERNABE</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>NICIO</t>
+  </si>
+  <si>
     <t>BARRAGAN</t>
   </si>
   <si>
@@ -91,12 +97,15 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>TORRES</t>
   </si>
   <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
     <t>VILLALBA</t>
   </si>
   <si>
@@ -116,6 +125,12 @@
   </si>
   <si>
     <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>ANDRES NOEL</t>
+  </si>
+  <si>
+    <t>JOSE JULIAN</t>
   </si>
   <si>
     <t>ADAN</t>
@@ -842,7 +857,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -880,10 +895,10 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -897,45 +912,45 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920337</v>
+        <v>20330051920363</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920340</v>
+        <v>20330051920025</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -943,39 +958,39 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920021</v>
+        <v>20330051920337</v>
       </c>
       <c r="B5" t="s">
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920336</v>
+        <v>20330051920340</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -984,27 +999,27 @@
         <v>11</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920345</v>
+        <v>20330051920021</v>
       </c>
       <c r="B7" t="s">
         <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1012,16 +1027,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920347</v>
+        <v>20330051920336</v>
       </c>
       <c r="B8" t="s">
         <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1030,6 +1045,52 @@
         <v>11</v>
       </c>
       <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>20330051920345</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>20330051920347</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Castro Vasquez Julieta - Estadisticos 20211.xlsx
+++ b/docentes/Castro Vasquez Julieta - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="33">
   <si>
     <t>Mat</t>
   </si>
@@ -73,82 +73,49 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>NICIO</t>
   </si>
   <si>
-    <t>BARRAGAN</t>
+    <t>VAZQUEZ</t>
   </si>
   <si>
     <t>CUEVAS</t>
   </si>
   <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>BACILIO</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>CASTELLANOS</t>
   </si>
   <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>VILLALBA</t>
+    <t>GOMEZ</t>
   </si>
   <si>
     <t>CUATRA</t>
   </si>
   <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>ATILANO</t>
-  </si>
-  <si>
-    <t>IXTLA</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>ANDRES NOEL</t>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
   </si>
   <si>
     <t>JOSE JULIAN</t>
   </si>
   <si>
-    <t>ADAN</t>
+    <t>ANGEL AMILCAR</t>
   </si>
   <si>
     <t>CESAR</t>
   </si>
   <si>
-    <t>OCTAVIO</t>
-  </si>
-  <si>
-    <t>YAIR</t>
-  </si>
-  <si>
-    <t>ELIEL</t>
-  </si>
-  <si>
-    <t>EVELYN</t>
+    <t>JAHEL</t>
+  </si>
+  <si>
+    <t>JENNIFER</t>
   </si>
 </sst>
 </file>
@@ -786,16 +753,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G2">
-        <v>55.56</v>
+        <v>58.33</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -812,16 +779,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>84.62</v>
+        <v>82.05</v>
       </c>
       <c r="H3">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -838,16 +805,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G4">
-        <v>45.83</v>
+        <v>66.67</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -857,7 +824,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -889,16 +856,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920003</v>
+        <v>20330051920025</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -907,21 +874,21 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920363</v>
+        <v>20330051920034</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -930,27 +897,27 @@
         <v>9</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920025</v>
+        <v>20330051920340</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -958,16 +925,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920337</v>
+        <v>20330051920354</v>
       </c>
       <c r="B5" t="s">
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -981,116 +948,24 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920340</v>
+        <v>20330051920223</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920021</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920336</v>
-      </c>
-      <c r="B8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920345</v>
-      </c>
-      <c r="B9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" t="s">
-        <v>42</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920347</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10">
         <v>1</v>
       </c>
     </row>
